--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561645369</v>
+        <v>46157.93070069454</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93070069454</v>
+        <v>46157.93152291528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93152291528</v>
+        <v>46157.93393336845</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393336845</v>
+        <v>46157.93707675581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93707675581</v>
+        <v>46158.28210360766</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210360766</v>
+        <v>46158.29665305338</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665305338</v>
+        <v>46158.29804417156</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804417156</v>
+        <v>46158.33381070298</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381070298</v>
+        <v>46158.36847460329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847460329</v>
+        <v>46158.37281297611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
